--- a/data/evaluation/task4/query_before_after.xlsx
+++ b/data/evaluation/task4/query_before_after.xlsx
@@ -1679,10 +1679,10 @@
         <v>0.913</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.927</v>
+        <v>0.929</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -1704,7 +1704,7 @@
         <v>0.803</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.912</v>
+        <v>0.915</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -1723,10 +1723,10 @@
         <v>0.927</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.833</v>
+        <v>0.827</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.917</v>
+        <v>0.919</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>

--- a/data/evaluation/task4/query_before_after.xlsx
+++ b/data/evaluation/task4/query_before_after.xlsx
@@ -1676,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.913</v>
+        <v>0.92</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.893</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.929</v>
+        <v>0.885</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -1701,10 +1701,10 @@
         <v>0.927</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.803</v>
+        <v>0.904</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.915</v>
+        <v>0.892</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -1720,16 +1720,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.927</v>
+        <v>0.92</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.827</v>
+        <v>0.908</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.919</v>
+        <v>0.878</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
     </row>
     <row r="5">
@@ -1745,13 +1745,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.827</v>
+        <v>0.931</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.912</v>
+        <v>0.874</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
+        <v>0.993</v>
       </c>
     </row>
   </sheetData>

--- a/data/evaluation/task4/query_before_after.xlsx
+++ b/data/evaluation/task4/query_before_after.xlsx
@@ -1676,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.92</v>
+        <v>0.913</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.893</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.885</v>
+        <v>0.921</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -1698,13 +1698,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.927</v>
+        <v>0.913</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.904</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.892</v>
+        <v>0.919</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -1720,16 +1720,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0.92</v>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>0.908</v>
-      </c>
       <c r="E4" s="2" t="n">
-        <v>0.878</v>
+        <v>0.894</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1742,16 +1742,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.931</v>
+        <v>0.92</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.874</v>
+        <v>0.892</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.993</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/evaluation/task4/query_before_after.xlsx
+++ b/data/evaluation/task4/query_before_after.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1554,6 +1554,358 @@
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>china+1; china plus one; 多地区布局; 分散生产; dual production; 原产地; 转运; 反规避; circumvention; transshipment; country of origin; substantial transformation; customs enforcement; 供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 市场准入; 合规; market access; regional requirement; customer access; 美国市场; 关税; us tariff</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>US tariff risk on Chinese EV batteries ; 对华关税 电池 加征 ; China EV battery supply chain dependency ; 电池 供应链 中间品 依赖 ; China EV battery manufacturing ecosystem ; 中国 电池 产业链 产能 ; EV battery manufacturing ecosystem ; 动力电池 产业链</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>tariff; supply_chain; china; battery; china_plus_one; us_market; eu_regulation; battery_sector</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>关税; tariff; 加征关税; section 301; 供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 中国; 国内生产; china; domestic production; manufacturing ecosystem; 动力电池; 电池材料; battery; lithium-ion; china+1; china plus one; 多地区布局; 分散生产; dual production; 美国市场; us tariff; market access</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>US export controls entity list battery ; 出口管制 实体清单 关联企业 ; US tariff risk on Chinese EV batteries ; 对华关税 电池 加征 ; China EV battery supply chain dependency ; 电池 供应链 中间品 依赖 ; 美国市场 准入 关税 电池 ; China+1 strategy dual production base</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>export_control; tariff; supply_chain; us_market; china_plus_one; china; eu_regulation; battery_sector; battery</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>出口管制; 实体清单; 两用物项; entity list; export control; affiliates rule; 关税; tariff; 加征关税; section 301; 供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 美国市场; us tariff; market access; customs enforcement; china+1; china plus one; 多地区布局; 分散生产; dual production; 中国; 国内生产</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性 雅保 Albemarle 最新年报如何披露其锂资源与转化加工的全球布局 以及相关的贸易政策风险</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>country of origin transshipment enforcement ; 反规避 原产地 转运 认定 ; US tariff risk on Chinese EV batteries ; 对华关税 电池 加征 ; China EV battery manufacturing ecosystem ; 中国 电池 产业链 产能 ; EV battery manufacturing ecosystem ; 动力电池 产业链</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>origin; tariff; china; battery; china_plus_one; us_market; eu_regulation; battery_sector; supply_chain</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>原产地; 转运; 反规避; circumvention; transshipment; country of origin; substantial transformation; customs enforcement; 关税; tariff; 加征关税; section 301; 中国; 国内生产; china; domestic production; manufacturing ecosystem; 动力电池; 电池材料; battery; lithium-ion; china+1; china plus one; 多地区布局; 分散生产; dual production; 美国市场; us tariff</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>中国产能布局 是否扩产 ; US tariff risk on Chinese EV batteries ; 对华关税 电池 加征 ; China+1 strategy dual production base ; China plus one 多地区布局 ; China EV battery manufacturing ecosystem ; 中国 电池 产业链 产能 ; 美国市场 准入 关税 电池</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>production_decision; tariff; china_plus_one; china; us_market; eu_regulation; battery_sector; battery; supply_chain</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>产能布局; 扩产; production footprint; capacity expansion; manufacturing base; 关税; tariff; 加征关税; section 301; china+1; china plus one; 多地区布局; 分散生产; dual production; 中国; 国内生产; china; domestic production; manufacturing ecosystem; 美国市场; us tariff; market access; customs enforcement; 欧盟电池法规; eu battery regulation; battery passport; carbon footprint; 动力电池</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>EV battery manufacturing ecosystem ; 动力电池 产业链</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>battery; battery_sector</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>动力电池; 电池材料; battery; lithium-ion; battery cell; cathode; anode</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>China manufacturing relocation to Southeast Asia ; 海外建厂 产能转移 东南亚 ; China EV battery supply chain dependency ; 电池 供应链 中间品 依赖 ; China EV battery manufacturing ecosystem ; 中国 电池 产业链 产能 ; China+1 strategy dual production base ; China plus one 多地区布局</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>relocation; supply_chain; china; china_plus_one; us_market; eu_regulation; battery_sector; battery</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>产能转移; 海外建厂; 生产基地; relocation; overseas production; southeast asia; 供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 中国; 国内生产; china; domestic production; manufacturing ecosystem; china+1; china plus one; 多地区布局; 分散生产; dual production; 美国市场; 关税; us tariff; market access; customs enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>China EV battery supply chain dependency ; 电池 供应链 中间品 依赖 ; EV battery manufacturing ecosystem ; 动力电池 产业链 ; US tariff risk on Chinese EV batteries ; 美国市场 准入 关税 电池 ; China+1 strategy dual production base ; China plus one 多地区布局</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain; battery; us_market; china_plus_one; china; eu_regulation; battery_sector</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 动力电池; 电池材料; battery; lithium-ion; 美国市场; 关税; us tariff; market access; customs enforcement; china+1; china plus one; 多地区布局; 分散生产; dual production; 中国; 国内生产; china; domestic production; manufacturing ecosystem; 欧盟电池法规; eu battery regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>China EV battery supply chain dependency ; 电池 供应链 中间品 依赖 ; China EV battery manufacturing ecosystem ; 中国 电池 产业链 产能 ; EV battery manufacturing ecosystem ; 动力电池 产业链 ; China+1 strategy dual production base ; China plus one 多地区布局</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain; china; battery; china_plus_one; us_market; eu_regulation; battery_sector</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 中国; 国内生产; china; domestic production; manufacturing ecosystem; 动力电池; 电池材料; battery; lithium-ion; china+1; china plus one; 多地区布局; 分散生产; dual production; 美国市场; 关税; us tariff; market access; customs enforcement; 欧盟电池法规; eu battery regulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>country of origin transshipment enforcement ; 反规避 原产地 转运 认定 ; China EV battery supply chain dependency ; 电池 供应链 中间品 依赖 ; China EV battery manufacturing ecosystem ; 中国 电池 产业链 产能 ; China+1 strategy dual production base ; China plus one 多地区布局</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>origin; supply_chain; china; china_plus_one; us_market; eu_regulation; battery_sector; battery</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>原产地; 转运; 反规避; circumvention; transshipment; country of origin; substantial transformation; customs enforcement; 供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 中国; 国内生产; china; domestic production; manufacturing ecosystem; china+1; china plus one; 多地区布局; 分散生产; dual production; 美国市场; 关税; us tariff</t>
         </is>
       </c>
     </row>
@@ -1676,13 +2028,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.913</v>
+        <v>0.8</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.893</v>
+        <v>0.916</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.93</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -1698,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.913</v>
+        <v>0.805</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.904</v>
+        <v>0.907</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.919</v>
+        <v>0.914</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -1720,13 +2072,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.907</v>
+        <v>0.83</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.92</v>
+        <v>0.927</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.894</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -1742,13 +2094,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="E5" s="2" t="n">
         <v>0.92</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.892</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>

--- a/data/evaluation/task4/query_before_after.xlsx
+++ b/data/evaluation/task4/query_before_after.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1906,6 +1906,118 @@
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>原产地; 转运; 反规避; circumvention; transshipment; country of origin; substantial transformation; customs enforcement; 供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 中国; 国内生产; china; domestic production; manufacturing ecosystem; china+1; china plus one; 多地区布局; 分散生产; dual production; 美国市场; 关税; us tariff</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>China EV battery supply chain dependency ; 电池 供应链 中间品 依赖 ; EV battery manufacturing ecosystem ; 动力电池 产业链 ; EU battery regulation compliance ; 欧盟电池法规 合规 ; China+1 strategy dual production base ; China plus one 多地区布局</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain; battery; eu_regulation; china_plus_one; china; us_market; battery_sector</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>供应链; 中间品; 供应商依赖; supply chain; intermediate inputs; supplier dependence; geographic concentration; 动力电池; 电池材料; battery; lithium-ion; 欧盟电池法规; eu battery regulation; battery passport; carbon footprint; china+1; china plus one; 多地区布局; 分散生产; dual production; 中国; 国内生产; china; domestic production; manufacturing ecosystem; 美国市场; 关税; us tariff</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>BYD production footprint ; BYD overseas factories ; BYD 产能布局 ; China EV battery manufacturing ecosystem ; 中国 电池 产业链 产能 ; EU battery regulation compliance ; 欧盟电池法规 合规 ; China+1 strategy dual production base</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>company_footprint; china; eu_regulation; china_plus_one; us_market; battery_sector; battery; supply_chain</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>BYD</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>BYD; production footprint; overseas factory; 产能布局; 海外基地; 中国; 国内生产; china; domestic production; manufacturing ecosystem; 欧盟电池法规; eu battery regulation; battery passport; carbon footprint; china+1; china plus one; 多地区布局; 分散生产; dual production; 美国市场; 关税; us tariff; market access; customs enforcement; 动力电池; 电池材料; battery cell; lithium-ion</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>中国产能布局 是否扩产 ; China EV battery manufacturing ecosystem ; 中国 电池 产业链 产能 ; EV battery manufacturing ecosystem ; 动力电池 产业链 ; EU battery regulation compliance ; 欧盟电池法规 合规 ; China+1 strategy dual production base</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>production_decision; china; battery; eu_regulation; china_plus_one; us_market; battery_sector; supply_chain</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>产能布局; 扩产; production footprint; capacity expansion; manufacturing base; 中国; 国内生产; china; domestic production; manufacturing ecosystem; 动力电池; 电池材料; battery; lithium-ion; 欧盟电池法规; eu battery regulation; battery passport; carbon footprint; china+1; china plus one; 多地区布局; 分散生产; dual production; 美国市场; 关税; us tariff; market access; customs enforcement</t>
         </is>
       </c>
     </row>
@@ -2028,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.8</v>
+        <v>0.777</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.916</v>
+        <v>0.921</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.93</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -2050,13 +2162,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.805</v>
+        <v>0.772</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.907</v>
+        <v>0.914</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.914</v>
+        <v>0.921</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -2072,13 +2184,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.83</v>
+        <v>0.805</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.927</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.904</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -2094,13 +2206,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.835</v>
+        <v>0.8</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.919</v>
+        <v>0.925</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>

--- a/data/evaluation/task4/query_before_after.xlsx
+++ b/data/evaluation/task4/query_before_after.xlsx
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.921</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -2162,13 +2162,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.772</v>
+        <v>0.777</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.914</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.921</v>
+        <v>0.922</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -2190,7 +2190,7 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.904</v>
+        <v>0.903</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -2212,7 +2212,7 @@
         <v>0.925</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.921</v>
+        <v>0.919</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>

--- a/data/evaluation/task4/query_before_after.xlsx
+++ b/data/evaluation/task4/query_before_after.xlsx
@@ -2140,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.772</v>
+        <v>0.763</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.921</v>
+        <v>0.905</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
@@ -2162,13 +2162,13 @@
         <v>0</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.777</v>
+        <v>0.772</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.914</v>
+        <v>0.909</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.922</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -2184,13 +2184,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.805</v>
+        <v>0.791</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.914</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.903</v>
+        <v>0.906</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
@@ -2206,13 +2206,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.8</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.925</v>
+        <v>0.907</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.919</v>
+        <v>0.921</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1</v>
